--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESWAR\Desktop\Employee-Evaluation-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CBB89F-3A7B-427E-984F-EC3724742139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE472775-6916-4036-970E-BFABE804A309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6216" yWindow="3360" windowWidth="16824" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="199">
   <si>
     <t>QuestionID</t>
   </si>
@@ -39,50 +40,648 @@
     <t>CorrectAnswer</t>
   </si>
   <si>
-    <t>emp1</t>
-  </si>
-  <si>
-    <t>app is working</t>
-  </si>
-  <si>
-    <t>appppn</t>
-  </si>
-  <si>
-    <t>uuuu</t>
-  </si>
-  <si>
     <t>Tags</t>
   </si>
   <si>
-    <t>dfd,df,shhd,dgd,dggd</t>
-  </si>
-  <si>
     <t>dfd</t>
   </si>
   <si>
-    <t>#Issue &gt; Security &gt; Authentication Timeout,#Issue &gt; Login &gt; Session Failure,#Issue &gt; Verification &gt; OTP Delay,#Issue &gt; Access &gt; Unauthorized Error</t>
-  </si>
-  <si>
     <t>#Issue &gt; UI &gt; Dark Mode Failure,#Issue &gt; Reports &gt; Blank Data</t>
   </si>
   <si>
     <t>#Issue &gt; Security &gt; Authentication Timeout,#Issue &gt; Login &gt; Session Failure</t>
   </si>
   <si>
-    <t>,#Issue &gt; Reports &gt; Blank Data</t>
+    <t>#Issue &gt; Billing &gt; Invoice &gt; Incorrect Charges,
+#Issue &gt; Education &gt; Portal &gt; Assignment Upload Failure,
+#Issue &gt; Logistics &gt; Delivery &gt; Tracking Delay,
+#Issue &gt; Technical &gt; Login &gt; Password Reset,
+#Issue &gt; Banking &gt; Payment &gt; Transaction Failure,
+#Issue &gt; Account &gt; Registration &gt; Account Creation Failure,
+#Issue &gt; Security &gt; Access &gt; Authentication Failure,
+#Issue &gt; Healthcare &gt; Appointment &gt; Schedule Conflict,
+#Issue &gt; Security &gt; Verification &gt; Authentication Timeout,
+#Issue &gt; System &gt; Database &gt; Synchronization Failure,
+#Issue &gt; Operations &gt; Workflow &gt; Manual Intervention Required,
+#Issue &gt; Infrastructure &gt; Network &gt; Timeout Error,</t>
+  </si>
+  <si>
+    <t>While using internal services, a subscriber connected to the Healthcare platform received incorrect billing totals during invoice generation when server maintenance interrupted connected services. Customer service representatives manually verified transactions to reduce additional complaints. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a subscriber in the Banking domain uploaded assignment files that disappeared from the education portal after payment gateway callbacks failed unexpectedly. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a subscriber in the Hospitality domain reported shipment tracking updates arriving several hours late because storage systems stopped processing uploaded files. Managers delayed approval processes because records inside the platform were no longer reliable. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a patient from the Education industry received incorrect billing totals during invoice generation after network interruptions affected backend communication. Managers delayed approval processes because records inside the platform were no longer reliable. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>While using internal services, a cashier connected to the Retail platform forgot email password and recovery verification failed when the regional database stopped replicating records. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a traveler from the Education industry noticed money deducted without payment confirmation after a failed cloud synchronization update. Customer service representatives manually verified transactions to reduce additional complaints. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a employee in the Travel domain reported shipment tracking updates arriving several hours late when authentication APIs returned incomplete responses. Several users reported similar complaints through the helpdesk portal during the same period. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>A cashier working in the Healthcare sector reported shipment tracking updates arriving several hours late after a failed cloud synchronization update. Managers delayed approval processes because records inside the platform were no longer reliable. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a customer in the Healthcare domain could not create a new account because registration forms crashed after a failed cloud synchronization update. Several users reported similar complaints through the helpdesk portal during the same period. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a traveler in the Telecom domain noticed money deducted without payment confirmation when authentication APIs returned incomplete responses. Managers delayed approval processes because records inside the platform were no longer reliable. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>A traveler working in the Healthcare sector could not create a new account because registration forms crashed when the regional database stopped replicating records. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>While using internal services, a student connected to the Technology platform forgot email password and recovery verification failed when the regional database stopped replicating records. Several users reported similar complaints through the helpdesk portal during the same period. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a employee from the Hospitality industry received incorrect billing totals during invoice generation when the regional database stopped replicating records. The user contacted support multiple times after receiving conflicting responses from different departments. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>A manager working in the Banking sector reported shipment tracking updates arriving several hours late when authentication APIs returned incomplete responses. Technical staff restarted dependent services after discovering incomplete synchronization events. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a manager in the Education domain reported shipment tracking updates arriving several hours late when the regional database stopped replicating records. Several users reported similar complaints through the helpdesk portal during the same period. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a manager from the Travel industry forgot email password and recovery verification failed after a failed cloud synchronization update. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a manager in the Retail domain received incorrect billing totals during invoice generation when server maintenance interrupted connected services. Several users reported similar complaints through the helpdesk portal during the same period. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a customer from the Healthcare industry received incorrect billing totals during invoice generation when authentication APIs returned incomplete responses. Technical staff restarted dependent services after discovering incomplete synchronization events. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>While using internal services, a student connected to the Hospitality platform forgot email password and recovery verification failed because session validation services timed out repeatedly. Managers delayed approval processes because records inside the platform were no longer reliable. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>A traveler working in the Technology sector could not create a new account because registration forms crashed because storage systems stopped processing uploaded files. Managers delayed approval processes because records inside the platform were no longer reliable. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>A manager working in the Banking sector reported shipment tracking updates arriving several hours late when the regional database stopped replicating records. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>While using internal services, a traveler connected to the Telecom platform received incorrect billing totals during invoice generation after payment gateway callbacks failed unexpectedly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>A customer working in the Technology sector forgot email password and recovery verification failed when authentication APIs returned incomplete responses. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a customer from the Healthcare industry lost account access after repeated authentication failures when the regional database stopped replicating records. Several users reported similar complaints through the helpdesk portal during the same period. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a employee in the Technology domain lost account access after repeated authentication failures after a failed cloud synchronization update. Technical staff restarted dependent services after discovering incomplete synchronization events. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a student from the Technology industry noticed money deducted without payment confirmation after a failed cloud synchronization update. Customer service representatives manually verified transactions to reduce additional complaints. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>A patient working in the Healthcare sector uploaded assignment files that disappeared from the education portal after network interruptions affected backend communication. Customer service representatives manually verified transactions to reduce additional complaints. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>While using internal services, a manager connected to the Travel platform uploaded assignment files that disappeared from the education portal after network interruptions affected backend communication. Managers delayed approval processes because records inside the platform were no longer reliable. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a employee from the Technology industry received incorrect billing totals during invoice generation because session validation services timed out repeatedly. Technical staff restarted dependent services after discovering incomplete synchronization events. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>While using internal services, a student connected to the Healthcare platform lost account access after repeated authentication failures when the regional database stopped replicating records. Managers delayed approval processes because records inside the platform were no longer reliable. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a patient from the Hospitality industry found duplicate hospital appointments assigned to different patients after payment gateway callbacks failed unexpectedly. Technical staff restarted dependent services after discovering incomplete synchronization events. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>A employee working in the Technology sector found duplicate hospital appointments assigned to different patients because storage systems stopped processing uploaded files. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>A cashier working in the Travel sector reported shipment tracking updates arriving several hours late when server maintenance interrupted connected services. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>A traveler working in the Telecom sector uploaded assignment files that disappeared from the education portal when authentication APIs returned incomplete responses. Technical staff restarted dependent services after discovering incomplete synchronization events. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>A patient working in the Hospitality sector uploaded assignment files that disappeared from the education portal when the regional database stopped replicating records. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a subscriber in the Banking domain received incorrect billing totals during invoice generation when server maintenance interrupted connected services. Technical staff restarted dependent services after discovering incomplete synchronization events. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a customer in the Healthcare domain lost account access after repeated authentication failures after a failed cloud synchronization update. The user contacted support multiple times after receiving conflicting responses from different departments. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>While using internal services, a customer connected to the Technology platform uploaded assignment files that disappeared from the education portal because session validation services timed out repeatedly. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a employee from the Hospitality industry uploaded assignment files that disappeared from the education portal because storage systems stopped processing uploaded files. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>While using internal services, a manager connected to the Retail platform reported shipment tracking updates arriving several hours late because session validation services timed out repeatedly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a traveler from the Travel industry reported shipment tracking updates arriving several hours late after payment gateway callbacks failed unexpectedly. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>A subscriber working in the Hospitality sector received incorrect billing totals during invoice generation when the regional database stopped replicating records. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a employee in the Hospitality domain noticed money deducted without payment confirmation after a failed cloud synchronization update. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a student in the Healthcare domain received incorrect billing totals during invoice generation because session validation services timed out repeatedly. Customer service representatives manually verified transactions to reduce additional complaints. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>While using internal services, a cashier connected to the Banking platform could not create a new account because registration forms crashed after payment gateway callbacks failed unexpectedly. Regional supervisors requested urgent escalation after normal business operations slowed significantly. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>A traveler working in the Hospitality sector received incorrect billing totals during invoice generation after a failed cloud synchronization update. Managers delayed approval processes because records inside the platform were no longer reliable. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a subscriber in the Technology domain forgot email password and recovery verification failed after a failed cloud synchronization update. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>While using internal services, a cashier connected to the Retail platform found duplicate hospital appointments assigned to different patients because storage systems stopped processing uploaded files. The user contacted support multiple times after receiving conflicting responses from different departments. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>A traveler working in the Hospitality sector noticed money deducted without payment confirmation after network interruptions affected backend communication. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>While using internal services, a manager connected to the Healthcare platform uploaded assignment files that disappeared from the education portal after payment gateway callbacks failed unexpectedly. Customer service representatives manually verified transactions to reduce additional complaints. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a patient in the Retail domain found duplicate hospital appointments assigned to different patients after a failed cloud synchronization update. Customer service representatives manually verified transactions to reduce additional complaints. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>A manager working in the Banking sector received incorrect billing totals during invoice generation because storage systems stopped processing uploaded files. Managers delayed approval processes because records inside the platform were no longer reliable. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>A employee working in the Hospitality sector noticed money deducted without payment confirmation because session validation services timed out repeatedly. Several users reported similar complaints through the helpdesk portal during the same period. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a manager from the Banking industry found duplicate hospital appointments assigned to different patients after a failed cloud synchronization update. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a student from the Healthcare industry reported shipment tracking updates arriving several hours late after a failed cloud synchronization update. Technical staff restarted dependent services after discovering incomplete synchronization events. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>A student working in the Retail sector could not create a new account because registration forms crashed after a failed cloud synchronization update. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a cashier in the Hospitality domain could not create a new account because registration forms crashed because storage systems stopped processing uploaded files. Several users reported similar complaints through the helpdesk portal during the same period. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a customer in the Banking domain could not create a new account because registration forms crashed when the regional database stopped replicating records. Several users reported similar complaints through the helpdesk portal during the same period. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>While using internal services, a employee connected to the Banking platform lost account access after repeated authentication failures after network interruptions affected backend communication. Several users reported similar complaints through the helpdesk portal during the same period. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a cashier from the Travel industry lost account access after repeated authentication failures when authentication APIs returned incomplete responses. Technical staff restarted dependent services after discovering incomplete synchronization events. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a manager in the Education domain forgot email password and recovery verification failed when authentication APIs returned incomplete responses. Managers delayed approval processes because records inside the platform were no longer reliable. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a subscriber from the Banking industry found duplicate hospital appointments assigned to different patients when authentication APIs returned incomplete responses. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>While using internal services, a student connected to the Technology platform lost account access after repeated authentication failures after a failed cloud synchronization update. Technical staff restarted dependent services after discovering incomplete synchronization events. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>SS20260514</t>
+  </si>
+  <si>
+    <t>SS20260515</t>
+  </si>
+  <si>
+    <t>SS20260516</t>
+  </si>
+  <si>
+    <t>SS20260517</t>
+  </si>
+  <si>
+    <t>SS20260518</t>
+  </si>
+  <si>
+    <t>SS20260519</t>
+  </si>
+  <si>
+    <t>SS20260520</t>
+  </si>
+  <si>
+    <t>SS20260521</t>
+  </si>
+  <si>
+    <t>SS20260522</t>
+  </si>
+  <si>
+    <t>SS20260523</t>
+  </si>
+  <si>
+    <t>SS20260524</t>
+  </si>
+  <si>
+    <t>SS20260525</t>
+  </si>
+  <si>
+    <t>SS20260526</t>
+  </si>
+  <si>
+    <t>SS20260527</t>
+  </si>
+  <si>
+    <t>SS20260528</t>
+  </si>
+  <si>
+    <t>SS20260529</t>
+  </si>
+  <si>
+    <t>SS20260530</t>
+  </si>
+  <si>
+    <t>SS20260531</t>
+  </si>
+  <si>
+    <t>SS20260532</t>
+  </si>
+  <si>
+    <t>SS20260533</t>
+  </si>
+  <si>
+    <t>SS20260534</t>
+  </si>
+  <si>
+    <t>SS20260535</t>
+  </si>
+  <si>
+    <t>SS20260536</t>
+  </si>
+  <si>
+    <t>SS20260537</t>
+  </si>
+  <si>
+    <t>SS20260538</t>
+  </si>
+  <si>
+    <t>SS20260539</t>
+  </si>
+  <si>
+    <t>SS20260540</t>
+  </si>
+  <si>
+    <t>SS20260541</t>
+  </si>
+  <si>
+    <t>SS20260542</t>
+  </si>
+  <si>
+    <t>SS20260543</t>
+  </si>
+  <si>
+    <t>SS20260544</t>
+  </si>
+  <si>
+    <t>SS20260545</t>
+  </si>
+  <si>
+    <t>SS20260546</t>
+  </si>
+  <si>
+    <t>SS20260547</t>
+  </si>
+  <si>
+    <t>SS20260548</t>
+  </si>
+  <si>
+    <t>SS20260549</t>
+  </si>
+  <si>
+    <t>SS20260550</t>
+  </si>
+  <si>
+    <t>SS20260551</t>
+  </si>
+  <si>
+    <t>SS20260552</t>
+  </si>
+  <si>
+    <t>SS20260553</t>
+  </si>
+  <si>
+    <t>SS20260554</t>
+  </si>
+  <si>
+    <t>SS20260555</t>
+  </si>
+  <si>
+    <t>SS20260556</t>
+  </si>
+  <si>
+    <t>SS20260557</t>
+  </si>
+  <si>
+    <t>SS20260558</t>
+  </si>
+  <si>
+    <t>SS20260559</t>
+  </si>
+  <si>
+    <t>SS20260560</t>
+  </si>
+  <si>
+    <t>SS20260561</t>
+  </si>
+  <si>
+    <t>SS20260562</t>
+  </si>
+  <si>
+    <t>SS20260563</t>
+  </si>
+  <si>
+    <t>SS20260564</t>
+  </si>
+  <si>
+    <t>SS20260565</t>
+  </si>
+  <si>
+    <t>SS20260566</t>
+  </si>
+  <si>
+    <t>SS20260567</t>
+  </si>
+  <si>
+    <t>SS20260568</t>
+  </si>
+  <si>
+    <t>SS20260569</t>
+  </si>
+  <si>
+    <t>SS20260570</t>
+  </si>
+  <si>
+    <t>SS20260571</t>
+  </si>
+  <si>
+    <t>SS20260572</t>
+  </si>
+  <si>
+    <t>SS20260573</t>
+  </si>
+  <si>
+    <t>SS20260574</t>
+  </si>
+  <si>
+    <t>SS20260575</t>
+  </si>
+  <si>
+    <t>SS20260576</t>
+  </si>
+  <si>
+    <t>SS20260577</t>
+  </si>
+  <si>
+    <t>SGS2610001</t>
+  </si>
+  <si>
+    <t>SS20260578</t>
+  </si>
+  <si>
+    <t>SS20260579</t>
+  </si>
+  <si>
+    <t>SS20260580</t>
+  </si>
+  <si>
+    <t>SS20260581</t>
+  </si>
+  <si>
+    <t>SS20260582</t>
+  </si>
+  <si>
+    <t>SS20260583</t>
+  </si>
+  <si>
+    <t>SS20260584</t>
+  </si>
+  <si>
+    <t>SS20260585</t>
+  </si>
+  <si>
+    <t>SS20260586</t>
+  </si>
+  <si>
+    <t>SS20260587</t>
+  </si>
+  <si>
+    <t>SS20260588</t>
+  </si>
+  <si>
+    <t>SS20260589</t>
+  </si>
+  <si>
+    <t>SS20260590</t>
+  </si>
+  <si>
+    <t>SS20260591</t>
+  </si>
+  <si>
+    <t>SS20260592</t>
+  </si>
+  <si>
+    <t>SS20260593</t>
+  </si>
+  <si>
+    <t>SS20260594</t>
+  </si>
+  <si>
+    <t>SS20260595</t>
+  </si>
+  <si>
+    <t>SS20260596</t>
+  </si>
+  <si>
+    <t>SS20260597</t>
+  </si>
+  <si>
+    <t>SS20260598</t>
+  </si>
+  <si>
+    <t>SS20260599</t>
+  </si>
+  <si>
+    <t>SS20260600</t>
+  </si>
+  <si>
+    <t>SS20260601</t>
+  </si>
+  <si>
+    <t>SS20260602</t>
+  </si>
+  <si>
+    <t>SGS2610002</t>
+  </si>
+  <si>
+    <t>During regular business operations, a subscriber from the Education industry reported shipment tracking updates arriving several hours late when server maintenance interrupted connected services. The user contacted support multiple times after receiving conflicting responses from different departments. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>While using internal services, a patient connected to the Healthcare platform forgot email password and recovery verification failed because storage systems stopped processing uploaded files. Managers delayed approval processes because records inside the platform were no longer reliable. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>A patient working in the Telecom sector uploaded assignment files that disappeared from the education portal after network interruptions affected backend communication. Several users reported similar complaints through the helpdesk portal during the same period. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a patient from the Telecom industry could not create a new account because registration forms crashed when server maintenance interrupted connected services. Several users reported similar complaints through the helpdesk portal during the same period. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a subscriber from the Telecom industry uploaded assignment files that disappeared from the education portal after a failed cloud synchronization update. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a cashier from the Education industry lost account access after repeated authentication failures because storage systems stopped processing uploaded files. Managers delayed approval processes because records inside the platform were no longer reliable. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>While using internal services, a cashier connected to the Banking platform received incorrect billing totals during invoice generation after payment gateway callbacks failed unexpectedly. Technical staff restarted dependent services after discovering incomplete synchronization events. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>A manager working in the Retail sector uploaded assignment files that disappeared from the education portal when authentication APIs returned incomplete responses. Several users reported similar complaints through the helpdesk portal during the same period. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a employee in the Telecom domain could not create a new account because registration forms crashed when the regional database stopped replicating records. Several users reported similar complaints through the helpdesk portal during the same period. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a patient from the Travel industry lost account access after repeated authentication failures when authentication APIs returned incomplete responses. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>A employee working in the Hospitality sector lost account access after repeated authentication failures after a failed cloud synchronization update. Technical staff restarted dependent services after discovering incomplete synchronization events. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a employee in the Education domain lost account access after repeated authentication failures after network interruptions affected backend communication. Regional supervisors requested urgent escalation after normal business operations slowed significantly. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>While using internal services, a customer connected to the Retail platform could not create a new account because registration forms crashed after a failed cloud synchronization update. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a traveler in the Travel domain received incorrect billing totals during invoice generation because session validation services timed out repeatedly. Several users reported similar complaints through the helpdesk portal during the same period. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>While using internal services, a employee connected to the Retail platform noticed money deducted without payment confirmation after a failed cloud synchronization update. Regional supervisors requested urgent escalation after normal business operations slowed significantly. The user contacted support multiple times after receiving conflicting responses from different departments.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a subscriber in the Healthcare domain found duplicate hospital appointments assigned to different patients after payment gateway callbacks failed unexpectedly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>A patient working in the Healthcare sector reported shipment tracking updates arriving several hours late when authentication APIs returned incomplete responses. Technical staff restarted dependent services after discovering incomplete synchronization events. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a customer in the Banking domain uploaded assignment files that disappeared from the education portal when authentication APIs returned incomplete responses. Customer service representatives manually verified transactions to reduce additional complaints. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a employee from the Education industry found duplicate hospital appointments assigned to different patients after network interruptions affected backend communication. Regional supervisors requested urgent escalation after normal business operations slowed significantly. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>While using internal services, a patient connected to the Telecom platform received incorrect billing totals during invoice generation when the regional database stopped replicating records. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>While using internal services, a customer connected to the Travel platform uploaded assignment files that disappeared from the education portal when server maintenance interrupted connected services. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Regional supervisors requested urgent escalation after normal business operations slowed significantly.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a manager from the Hospitality industry forgot email password and recovery verification failed when authentication APIs returned incomplete responses. Customer service representatives manually verified transactions to reduce additional complaints. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a patient in the Education domain noticed money deducted without payment confirmation when the regional database stopped replicating records. Technical staff restarted dependent services after discovering incomplete synchronization events. Managers delayed approval processes because records inside the platform were no longer reliable.</t>
+  </si>
+  <si>
+    <t>A subscriber working in the Travel sector lost account access after repeated authentication failures after payment gateway callbacks failed unexpectedly. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs. Audit teams documented the incident because automated monitoring alerts continued appearing unexpectedly.</t>
+  </si>
+  <si>
+    <t>While using internal services, a cashier connected to the Retail platform noticed money deducted without payment confirmation when authentication APIs returned incomplete responses. Customer service representatives manually verified transactions to reduce additional complaints. Several users reported similar complaints through the helpdesk portal during the same period.</t>
+  </si>
+  <si>
+    <t>A traveler working in the Hospitality sector forgot email password and recovery verification failed after payment gateway callbacks failed unexpectedly. The user contacted support multiple times after receiving conflicting responses from different departments. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>During regular business operations, a subscriber from the Telecom industry uploaded assignment files that disappeared from the education portal because session validation services timed out repeatedly. Managers delayed approval processes because records inside the platform were no longer reliable. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>A patient working in the Travel sector forgot email password and recovery verification failed when the regional database stopped replicating records. Several users reported similar complaints through the helpdesk portal during the same period. Operations teams switched temporarily to manual workflows while engineers inspected system activity logs.</t>
+  </si>
+  <si>
+    <t>An incident was reported when a student in the Education domain uploaded assignment files that disappeared from the education portal when server maintenance interrupted connected services. Managers delayed approval processes because records inside the platform were no longer reliable. Customer service representatives manually verified transactions to reduce additional complaints.</t>
+  </si>
+  <si>
+    <t>While using internal services, a employee connected to the Travel platform forgot email password and recovery verification failed after network interruptions affected backend communication. Customer service representatives manually verified transactions to reduce additional complaints. Technical staff restarted dependent services after discovering incomplete synchronization events.</t>
+  </si>
+  <si>
+    <t>SS20260603</t>
+  </si>
+  <si>
+    <t>SS20260604</t>
+  </si>
+  <si>
+    <t>SS20260605</t>
+  </si>
+  <si>
+    <t>SS20260606</t>
+  </si>
+  <si>
+    <t>SS20260607</t>
+  </si>
+  <si>
+    <t>"#Issue &gt; Billing &gt; Invoice &gt; Incorrect Charges,
+ #Issue &gt; Education &gt; Portal &gt; Assignment Upload Failure,
+ #Issue &gt; Logistics &gt; Delivery &gt; Tracking Delay,
+ #Issue &gt; Technical &gt; Login &gt; Password Reset,
+ #Issue &gt; Banking &gt; Payment &gt; Transaction Failure,
+ #Issue &gt; Account &gt; Registration &gt; Account Creation Failure,
+ #Issue &gt; Security &gt; Access &gt; Authentication Failure,
+ #Issue &gt; Healthcare &gt; Appointment &gt; Schedule Conflict,
+ #Issue &gt; Security &gt; Verification &gt; Authentication Timeout,
+ #Issue &gt; System &gt; Database &gt; Synchronization Failure,
+ #Issue &gt; Operations &gt; Workflow &gt; Manual Intervention Required,
+ #Issue &gt; Infrastructure &gt; Network &gt; Timeout Error,"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,7 +692,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,12 +700,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,10 +1011,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" customWidth="1"/>
+    <col min="3" max="3" width="61.109375" customWidth="1"/>
+    <col min="4" max="4" width="64.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,64 +1031,1374 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5D220B-C312-431A-BFB4-B7763A9579CA}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="76" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+        <v>162</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
+        <v>162</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
+        <v>162</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>